--- a/results/canaliculi/682_z29c1-3/measurements.xlsx
+++ b/results/canaliculi/682_z29c1-3/measurements.xlsx
@@ -433,6 +433,11 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>assignment_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +451,11 @@
       <c r="C2" t="n">
         <v>11</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,13 +503,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53.5455</v>
+        <v>33.8182</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>55.9792</v>
+        <v>33.3791</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -517,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>138.1376</v>
+        <v>85.2689</v>
       </c>
       <c r="C7" t="n">
-        <v>114.4376</v>
+        <v>75.6734</v>
       </c>
       <c r="D7" t="n">
-        <v>83.63939999999999</v>
+        <v>72.29649999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
-        <v>27282.0825</v>
+        <v>20923.1549</v>
       </c>
       <c r="D2" t="n">
-        <v>218.2567</v>
+        <v>252.0862</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -607,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>13476.435</v>
+        <v>6438.9103</v>
       </c>
       <c r="D3" t="n">
-        <v>166.3757</v>
+        <v>112.9633</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -629,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="C4" t="n">
-        <v>65517.4271</v>
+        <v>28442.2371</v>
       </c>
       <c r="D4" t="n">
-        <v>341.2366</v>
+        <v>258.5658</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -651,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>25397.1809</v>
+        <v>12782.1016</v>
       </c>
       <c r="D5" t="n">
-        <v>220.8451</v>
+        <v>163.8731</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -673,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>8209.4292</v>
+        <v>1839.8398</v>
       </c>
       <c r="D6" t="n">
-        <v>164.1886</v>
+        <v>87.6114</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -695,13 +705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>3547.5668</v>
+        <v>2000.1606</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4376</v>
+        <v>83.34</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>5457.1833</v>
+        <v>1156.7077</v>
       </c>
       <c r="D8" t="n">
-        <v>194.8994</v>
+        <v>64.2615</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -739,13 +749,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>3491.6623</v>
+        <v>1589.1413</v>
       </c>
       <c r="D9" t="n">
-        <v>112.6343</v>
+        <v>75.6734</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +771,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>735.2986</v>
+        <v>261.1249</v>
       </c>
       <c r="D10" t="n">
-        <v>61.2749</v>
+        <v>29.0139</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>791.7544</v>
+        <v>336.2498</v>
       </c>
       <c r="D11" t="n">
-        <v>71.9777</v>
+        <v>42.0312</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,13 +815,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>979.5656</v>
+        <v>166.5391</v>
       </c>
       <c r="D12" t="n">
-        <v>61.2228</v>
+        <v>16.6539</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -827,13 +837,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>2474.0967</v>
+        <v>666.8011</v>
       </c>
       <c r="D13" t="n">
-        <v>117.8141</v>
+        <v>44.4534</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -849,13 +859,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>2537.6652</v>
+        <v>451.7889</v>
       </c>
       <c r="D14" t="n">
-        <v>87.5057</v>
+        <v>23.7784</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>

--- a/results/canaliculi/682_z29c1-3/measurements.xlsx
+++ b/results/canaliculi/682_z29c1-3/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>graph</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>33.8182</v>
-      </c>
-      <c r="C6" t="n">
-        <v>21</v>
-      </c>
-      <c r="D6" t="n">
-        <v>33.3791</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>11</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>13.5455</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13.0489</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>457.9699</v>
+      </c>
+      <c r="C8" t="n">
+        <v>336.664</v>
+      </c>
+      <c r="D8" t="n">
+        <v>418.0035</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>85.2689</v>
-      </c>
-      <c r="C7" t="n">
-        <v>75.6734</v>
-      </c>
-      <c r="D7" t="n">
-        <v>72.29649999999999</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>38.1248</v>
+      </c>
+      <c r="C9" t="n">
+        <v>36.5707</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13.5454</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>20923.1549</v>
+        <v>101.669</v>
       </c>
       <c r="D2" t="n">
-        <v>252.0862</v>
+        <v>33.8897</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>6438.9103</v>
+        <v>808.595</v>
       </c>
       <c r="D3" t="n">
-        <v>112.9633</v>
+        <v>28.8784</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>28442.2371</v>
+        <v>173.468</v>
       </c>
       <c r="D4" t="n">
-        <v>258.5658</v>
+        <v>19.2742</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>12782.1016</v>
+        <v>1536.9281</v>
       </c>
       <c r="D5" t="n">
-        <v>163.8731</v>
+        <v>33.4115</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>1839.8398</v>
+        <v>197.669</v>
       </c>
       <c r="D6" t="n">
-        <v>87.6114</v>
+        <v>65.8897</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>2000.1606</v>
+        <v>636.3452</v>
       </c>
       <c r="D7" t="n">
-        <v>83.34</v>
+        <v>37.4321</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>1156.7077</v>
+        <v>670.6711</v>
       </c>
       <c r="D8" t="n">
-        <v>64.2615</v>
+        <v>22.3557</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1589.1413</v>
+        <v>368.7645</v>
       </c>
       <c r="D9" t="n">
-        <v>75.6734</v>
+        <v>26.3403</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>261.1249</v>
+        <v>255.9949</v>
       </c>
       <c r="D10" t="n">
-        <v>29.0139</v>
+        <v>36.5707</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>336.2498</v>
+        <v>336.664</v>
       </c>
       <c r="D11" t="n">
-        <v>42.0312</v>
+        <v>56.1107</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -815,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>166.5391</v>
+        <v>89.15430000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>16.6539</v>
+        <v>44.5772</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -837,13 +888,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>666.8011</v>
+        <v>459.262</v>
       </c>
       <c r="D13" t="n">
-        <v>44.4534</v>
+        <v>41.7511</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -859,13 +910,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>451.7889</v>
+        <v>174.8234</v>
       </c>
       <c r="D14" t="n">
-        <v>23.7784</v>
+        <v>29.1372</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>

--- a/results/canaliculi/682_z29c1-3/measurements.xlsx
+++ b/results/canaliculi/682_z29c1-3/measurements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="per_lacuna" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_lacuna" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,13 +531,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.5455</v>
+        <v>26.1818</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>13.0489</v>
+        <v>22.1667</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -554,13 +555,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>457.9699</v>
+        <v>848.5146</v>
       </c>
       <c r="C8" t="n">
-        <v>336.664</v>
+        <v>799.7838</v>
       </c>
       <c r="D8" t="n">
-        <v>418.0035</v>
+        <v>602.7154</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -578,13 +579,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.1248</v>
+        <v>38.2007</v>
       </c>
       <c r="C9" t="n">
-        <v>36.5707</v>
+        <v>36.5334</v>
       </c>
       <c r="D9" t="n">
-        <v>13.5454</v>
+        <v>13.1105</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -606,6 +607,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>per-field metrics -- independent of the per-lacuna assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only ~23% of skeleton length is graph-connected to any lacuna in these 2D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sections, so per-cell numbers use a quarter of the network. These use all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analysed_area_px2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1023566</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_skeleton_length_px</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>38368</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_per_px</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03748464</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>junction_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>485</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junction_density_per_px2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00047383</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lacuna_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lacunae_per_px2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeleton_component_count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>707</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mean_component_length_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>54.2687</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>median_component_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -649,10 +850,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>101.669</v>
+        <v>102.669</v>
       </c>
       <c r="D2" t="n">
-        <v>33.8897</v>
+        <v>34.223</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -668,13 +869,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>808.595</v>
+        <v>1038.8032</v>
       </c>
       <c r="D3" t="n">
-        <v>28.8784</v>
+        <v>29.6801</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -690,13 +891,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
-        <v>173.468</v>
+        <v>1414.5433</v>
       </c>
       <c r="D4" t="n">
-        <v>19.2742</v>
+        <v>23.1892</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -712,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C5" t="n">
-        <v>1536.9281</v>
+        <v>2207.055</v>
       </c>
       <c r="D5" t="n">
-        <v>33.4115</v>
+        <v>31.0853</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -734,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>197.669</v>
+        <v>799.7838</v>
       </c>
       <c r="D6" t="n">
-        <v>65.8897</v>
+        <v>36.3538</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -756,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>636.3452</v>
+        <v>840.2691</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4321</v>
+        <v>36.5334</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -778,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
-        <v>670.6711</v>
+        <v>857.1686</v>
       </c>
       <c r="D8" t="n">
-        <v>22.3557</v>
+        <v>23.1667</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -800,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>368.7645</v>
+        <v>1252.46</v>
       </c>
       <c r="D9" t="n">
-        <v>26.3403</v>
+        <v>39.1394</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -822,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>255.9949</v>
+        <v>410.6346</v>
       </c>
       <c r="D10" t="n">
-        <v>36.5707</v>
+        <v>37.3304</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -844,13 +1045,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>336.664</v>
+        <v>405.4335</v>
       </c>
       <c r="D11" t="n">
-        <v>56.1107</v>
+        <v>40.5434</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -866,13 +1067,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>89.15430000000001</v>
+        <v>213.7939</v>
       </c>
       <c r="D12" t="n">
-        <v>44.5772</v>
+        <v>71.2646</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -888,13 +1089,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>459.262</v>
+        <v>490.0904</v>
       </c>
       <c r="D13" t="n">
-        <v>41.7511</v>
+        <v>49.009</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -910,13 +1111,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>174.8234</v>
+        <v>260.7939</v>
       </c>
       <c r="D14" t="n">
-        <v>29.1372</v>
+        <v>26.0794</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
